--- a/artfynd/A 10694-2021 artfynd.xlsx
+++ b/artfynd/A 10694-2021 artfynd.xlsx
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119779378</v>
+        <v>119779382</v>
       </c>
       <c r="B3" t="n">
-        <v>57218</v>
+        <v>57226</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,20 +815,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100082</v>
+        <v>100067</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -838,14 +838,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119779382</v>
+        <v>119779378</v>
       </c>
       <c r="B4" t="n">
-        <v>57226</v>
+        <v>57218</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,20 +939,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100067</v>
+        <v>100082</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -962,14 +962,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>

--- a/artfynd/A 10694-2021 artfynd.xlsx
+++ b/artfynd/A 10694-2021 artfynd.xlsx
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119779382</v>
+        <v>119779376</v>
       </c>
       <c r="B3" t="n">
-        <v>57226</v>
+        <v>56660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,33 +819,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100067</v>
+        <v>102104</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Smådopping</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Tachybaptus ruficollis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119779376</v>
+        <v>119779382</v>
       </c>
       <c r="B5" t="n">
-        <v>56660</v>
+        <v>57226</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,33 +1067,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102104</v>
+        <v>100067</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smådopping</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tachybaptus ruficollis</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>

--- a/artfynd/A 10694-2021 artfynd.xlsx
+++ b/artfynd/A 10694-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119779394</v>
+        <v>119779382</v>
       </c>
       <c r="B2" t="n">
-        <v>57208</v>
+        <v>57226</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100034</v>
+        <v>100067</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå kärrhök</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Circus cyaneus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1766)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>förbiflygande</t>
@@ -803,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119779376</v>
+        <v>119779378</v>
       </c>
       <c r="B3" t="n">
-        <v>56660</v>
+        <v>57218</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,30 +811,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102104</v>
+        <v>100082</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smådopping</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tachybaptus ruficollis</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -927,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119779378</v>
+        <v>119779376</v>
       </c>
       <c r="B4" t="n">
-        <v>57218</v>
+        <v>56660</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,30 +935,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100082</v>
+        <v>102104</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Smådopping</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Tachybaptus ruficollis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -1051,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119779382</v>
+        <v>119779394</v>
       </c>
       <c r="B5" t="n">
-        <v>57226</v>
+        <v>57208</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,30 +1063,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100067</v>
+        <v>100034</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Blå kärrhök</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Circus cyaneus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Linnaeus, 1766)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>förbiflygande</t>

--- a/artfynd/A 10694-2021 artfynd.xlsx
+++ b/artfynd/A 10694-2021 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119779378</v>
+        <v>119779376</v>
       </c>
       <c r="B3" t="n">
-        <v>57218</v>
+        <v>56660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,30 +811,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100082</v>
+        <v>102104</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Smådopping</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Tachybaptus ruficollis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119779376</v>
+        <v>119779378</v>
       </c>
       <c r="B4" t="n">
-        <v>56660</v>
+        <v>57218</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,30 +935,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102104</v>
+        <v>100082</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smådopping</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tachybaptus ruficollis</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>

--- a/artfynd/A 10694-2021 artfynd.xlsx
+++ b/artfynd/A 10694-2021 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119779376</v>
+        <v>119779378</v>
       </c>
       <c r="B3" t="n">
-        <v>56660</v>
+        <v>57218</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,30 +811,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102104</v>
+        <v>100082</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smådopping</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tachybaptus ruficollis</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119779378</v>
+        <v>119779376</v>
       </c>
       <c r="B4" t="n">
-        <v>57218</v>
+        <v>56660</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,30 +935,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100082</v>
+        <v>102104</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Smådopping</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Tachybaptus ruficollis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>

--- a/artfynd/A 10694-2021 artfynd.xlsx
+++ b/artfynd/A 10694-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119779382</v>
       </c>
       <c r="B2" t="n">
-        <v>57226</v>
+        <v>57236</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119779378</v>
+        <v>119779394</v>
       </c>
       <c r="B3" t="n">
         <v>57218</v>
@@ -811,37 +811,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100082</v>
+        <v>100034</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Blå kärrhök</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Circus cyaneus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Linnaeus, 1766)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -923,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119779376</v>
+        <v>119779378</v>
       </c>
       <c r="B4" t="n">
-        <v>56660</v>
+        <v>57228</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,30 +939,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102104</v>
+        <v>100082</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smådopping</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tachybaptus ruficollis</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -1047,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119779394</v>
+        <v>119779376</v>
       </c>
       <c r="B5" t="n">
-        <v>57208</v>
+        <v>56670</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,37 +1067,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100034</v>
+        <v>102104</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå kärrhök</t>
+          <t>Smådopping</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Circus cyaneus</t>
+          <t>Tachybaptus ruficollis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1766)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>

--- a/artfynd/A 10694-2021 artfynd.xlsx
+++ b/artfynd/A 10694-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1173,6 +1173,263 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121870234</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57866</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>233849</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svarthakad buskskvätta</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Saxicola rubicola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1766)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Allarpsmaden, V Gärdslöv, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>399187</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6148264</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Trelleborg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gärdslöv</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Vid parkeringen</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Gabriella Håkansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Gabriella Håkansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121870481</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56468</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102932</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kricka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Anas crecca</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Allarpsmaden, V Gärdslöv, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>399187</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6148264</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Trelleborg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gärdslöv</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Gabriella Håkansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Gabriella Håkansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10694-2021 artfynd.xlsx
+++ b/artfynd/A 10694-2021 artfynd.xlsx
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121870234</v>
+        <v>121870481</v>
       </c>
       <c r="B6" t="n">
-        <v>57866</v>
+        <v>56468</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,37 +1191,33 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>233849</v>
+        <v>102932</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svarthakad buskskvätta</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saxicola rubicola</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1766)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1266,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1276,12 +1272,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Vid parkeringen</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1308,10 +1299,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121870481</v>
+        <v>121870234</v>
       </c>
       <c r="B7" t="n">
-        <v>56468</v>
+        <v>57866</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1324,33 +1315,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102932</v>
+        <v>233849</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Svarthakad buskskvätta</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Saxicola rubicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1766)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1395,7 +1390,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1405,7 +1400,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Vid parkeringen</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 10694-2021 artfynd.xlsx
+++ b/artfynd/A 10694-2021 artfynd.xlsx
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121870481</v>
+        <v>121870234</v>
       </c>
       <c r="B6" t="n">
-        <v>56468</v>
+        <v>57866</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,33 +1191,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102932</v>
+        <v>233849</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Svarthakad buskskvätta</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Saxicola rubicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1766)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1262,7 +1266,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,7 +1276,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Vid parkeringen</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1299,10 +1308,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121870234</v>
+        <v>121870481</v>
       </c>
       <c r="B7" t="n">
-        <v>57866</v>
+        <v>56468</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1315,37 +1324,33 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>233849</v>
+        <v>102932</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svarthakad buskskvätta</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saxicola rubicola</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1766)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1390,7 +1395,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1400,12 +1405,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Vid parkeringen</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 10694-2021 artfynd.xlsx
+++ b/artfynd/A 10694-2021 artfynd.xlsx
@@ -1178,7 +1178,7 @@
         <v>121870234</v>
       </c>
       <c r="B6" t="n">
-        <v>57866</v>
+        <v>57874</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>121870481</v>
       </c>
       <c r="B7" t="n">
-        <v>56468</v>
+        <v>56476</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 10694-2021 artfynd.xlsx
+++ b/artfynd/A 10694-2021 artfynd.xlsx
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121870234</v>
+        <v>121870481</v>
       </c>
       <c r="B6" t="n">
-        <v>57874</v>
+        <v>56476</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,37 +1191,33 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>233849</v>
+        <v>102932</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svarthakad buskskvätta</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saxicola rubicola</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1766)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1266,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1276,12 +1272,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Vid parkeringen</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1308,10 +1299,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121870481</v>
+        <v>121870234</v>
       </c>
       <c r="B7" t="n">
-        <v>56476</v>
+        <v>57874</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1324,33 +1315,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102932</v>
+        <v>233849</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Svarthakad buskskvätta</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Saxicola rubicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1766)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1395,7 +1390,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1405,7 +1400,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Vid parkeringen</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 10694-2021 artfynd.xlsx
+++ b/artfynd/A 10694-2021 artfynd.xlsx
@@ -1178,7 +1178,7 @@
         <v>121870481</v>
       </c>
       <c r="B6" t="n">
-        <v>56476</v>
+        <v>56480</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>121870234</v>
       </c>
       <c r="B7" t="n">
-        <v>57874</v>
+        <v>57878</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 10694-2021 artfynd.xlsx
+++ b/artfynd/A 10694-2021 artfynd.xlsx
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121870234</v>
+        <v>121870481</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>56483</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,37 +1191,33 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>233849</v>
+        <v>102932</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svarthakad buskskvätta</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saxicola rubicola</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1766)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1266,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1276,12 +1272,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Vid parkeringen</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1308,10 +1299,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121870481</v>
+        <v>121870234</v>
       </c>
       <c r="B7" t="n">
-        <v>56483</v>
+        <v>57884</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1324,33 +1315,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102932</v>
+        <v>233849</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Svarthakad buskskvätta</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Saxicola rubicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1766)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1395,7 +1390,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1405,7 +1400,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Vid parkeringen</t>
         </is>
       </c>
       <c r="AD7" t="b">
